--- a/IB/2/График.xlsx
+++ b/IB/2/График.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Labs_6\IB\2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA77FC60-65E8-4191-BE1E-7E4F56C67E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1E6B4E-E9EC-49E9-B0BF-FB241E0DE9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5A640D21-0A41-4D13-BEE8-F10C6CB8E9B7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
   <si>
     <t>а</t>
   </si>
@@ -219,9 +219,6 @@
   </si>
   <si>
     <t>z</t>
-  </si>
-  <si>
-    <t>ź</t>
   </si>
 </sst>
 </file>
@@ -433,94 +430,94 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
+                  <c:v>282</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>16</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="7">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>312</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>164</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>154</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>216</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="25">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="29">
-                  <c:v>1</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -746,94 +743,94 @@
                   <c:v>a</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>a</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>ą</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>b</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>c</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>ć</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>d</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>e</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>ę</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>f</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>g</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>h</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>i</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>j</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>k</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>l</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>ł</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>m</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>n</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>ń</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>ó</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>p</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="23">
                   <c:v>r</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="24">
                   <c:v>s</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="25">
                   <c:v>ś</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>t</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>u</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>w</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>y</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>z</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>ź</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -848,94 +845,94 @@
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>216</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>186</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="10">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>3</c:v>
-                </c:pt>
                 <c:pt idx="20">
-                  <c:v>4</c:v>
+                  <c:v>206</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1</c:v>
+                  <c:v>144</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1</c:v>
+                  <c:v>126</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4</c:v>
+                  <c:v>144</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2</c:v>
+                  <c:v>116</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2</c:v>
+                  <c:v>134</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2606,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>16</v>
+        <v>282</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
@@ -2621,14 +2618,14 @@
         <v>2</v>
       </c>
       <c r="B2" s="1">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>1</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -2636,14 +2633,14 @@
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3" s="1">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2651,14 +2648,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2666,14 +2663,14 @@
         <v>8</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2681,14 +2678,14 @@
         <v>10</v>
       </c>
       <c r="B6" s="1">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2696,14 +2693,14 @@
         <v>12</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2711,14 +2708,14 @@
         <v>14</v>
       </c>
       <c r="B8" s="1">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1">
-        <v>2</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2726,14 +2723,14 @@
         <v>16</v>
       </c>
       <c r="B9" s="1">
-        <v>7</v>
+        <v>312</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2741,14 +2738,14 @@
         <v>18</v>
       </c>
       <c r="B10" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2756,14 +2753,14 @@
         <v>20</v>
       </c>
       <c r="B11" s="1">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E11" s="1">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2771,14 +2768,14 @@
         <v>22</v>
       </c>
       <c r="B12" s="1">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2786,14 +2783,14 @@
         <v>24</v>
       </c>
       <c r="B13" s="1">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E13" s="1">
-        <v>2</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2801,14 +2798,14 @@
         <v>26</v>
       </c>
       <c r="B14" s="1">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1">
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2816,14 +2813,14 @@
         <v>28</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>214</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2831,14 +2828,14 @@
         <v>30</v>
       </c>
       <c r="B16" s="1">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E16" s="1">
-        <v>2</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2846,14 +2843,14 @@
         <v>32</v>
       </c>
       <c r="B17" s="1">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2861,14 +2858,14 @@
         <v>34</v>
       </c>
       <c r="B18" s="1">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2876,14 +2873,14 @@
         <v>36</v>
       </c>
       <c r="B19" s="1">
-        <v>10</v>
+        <v>216</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E19" s="1">
-        <v>1</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -2891,14 +2888,14 @@
         <v>38</v>
       </c>
       <c r="B20" s="1">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E20" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2906,14 +2903,14 @@
         <v>40</v>
       </c>
       <c r="B21" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E21" s="1">
-        <v>4</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2921,14 +2918,14 @@
         <v>42</v>
       </c>
       <c r="B22" s="1">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E22" s="1">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -2936,14 +2933,14 @@
         <v>44</v>
       </c>
       <c r="B23" s="1">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E23" s="1">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -2951,14 +2948,14 @@
         <v>46</v>
       </c>
       <c r="B24" s="1">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E24" s="1">
-        <v>1</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2966,14 +2963,14 @@
         <v>48</v>
       </c>
       <c r="B25" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E25" s="1">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -2981,14 +2978,14 @@
         <v>50</v>
       </c>
       <c r="B26" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E26" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2996,14 +2993,14 @@
         <v>52</v>
       </c>
       <c r="B27" s="1">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E27" s="1">
-        <v>1</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3011,14 +3008,14 @@
         <v>54</v>
       </c>
       <c r="B28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E28" s="1">
-        <v>4</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3026,14 +3023,14 @@
         <v>56</v>
       </c>
       <c r="B29" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E29" s="1">
-        <v>4</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3041,14 +3038,14 @@
         <v>58</v>
       </c>
       <c r="B30" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E30" s="1">
-        <v>2</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3056,10 +3053,10 @@
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" s="1">
-        <v>2</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
